--- a/artfynd/A 25660-2025 artfynd.xlsx
+++ b/artfynd/A 25660-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,6 +794,123 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127780010</v>
+      </c>
+      <c r="B3" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>655000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6648767</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25660-2025 artfynd.xlsx
+++ b/artfynd/A 25660-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>77318300</v>
       </c>
       <c r="B2" t="n">
-        <v>93056</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655104.768038649</v>
+        <v>655105</v>
       </c>
       <c r="R2" t="n">
-        <v>6648797.882854831</v>
+        <v>6648798</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2019-04-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-04-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +784,7 @@
         <v>127780010</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,6 +895,110 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>77318224</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tomta, 1,0 km SV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>654952</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6648635</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
